--- a/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="177">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -483,6 +483,9 @@
     <t>Valeur du resultat</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
     <t>Statut de grossesse de la patiente (enceinte, pas enceinte, etc.)</t>
   </si>
   <si>
@@ -554,25 +557,13 @@
 </t>
   </si>
   <si>
-    <t>Observation associée a la date d'accouchement</t>
-  </si>
-  <si>
-    <t>jdv-date-accouchement-cisis (1.2.250.1.213.1.1.5.853)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-date-accouchement-cisis|20260619134042</t>
+    <t>Observation associée a la date d'accouchement. Le type de l'observation doit être issu du jeu de valeurs jdv-date-accouchement-cisis (1.2.250.1.213.1.1.5.853) : https://smt.esante.gouv.fr/fhir/ValueSet/jdv-date-accouchement-cisis</t>
   </si>
   <si>
     <t>fr-lm-pregnancy-status.hasMember[x].hasMemberGestationalAge</t>
   </si>
   <si>
-    <t>Observation associée a l'age gestationnel</t>
-  </si>
-  <si>
-    <t>jdv-age-gestationnel-cisis (1.2.250.1.213.1.1.5.854)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-age-gestationnel-cisis|20260619134042</t>
+    <t>Observation associée a l'age gestationnel. Le type de l'observation doit être issu du jeu de valeurs jdv-age-gestationnel-cisis (1.2.250.1.213.1.1.5.854) : https://smt.esante.gouv.fr/fhir/ValueSet/jdv-age-gestationnel-cisis</t>
   </si>
 </sst>
 </file>
@@ -902,7 +893,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.4765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.75" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.0625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -3185,13 +3176,13 @@
         <v>73</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>73</v>
@@ -3226,10 +3217,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3255,10 +3246,10 @@
         <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3309,7 +3300,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3326,10 +3317,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3352,13 +3343,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3409,7 +3400,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3426,10 +3417,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3452,13 +3443,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3509,7 +3500,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3526,10 +3517,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3555,10 +3546,10 @@
         <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3609,7 +3600,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3626,10 +3617,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3652,13 +3643,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3709,7 +3700,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3726,10 +3717,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3755,10 +3746,10 @@
         <v>80</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3809,7 +3800,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3826,10 +3817,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3852,13 +3843,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3909,7 +3900,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3926,10 +3917,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3952,13 +3943,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -3988,10 +3979,10 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>73</v>
@@ -4009,7 +4000,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4026,10 +4017,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4052,13 +4043,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4088,10 +4079,10 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>179</v>
+        <v>73</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>73</v>
@@ -4109,7 +4100,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
